--- a/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
@@ -1502,7 +1502,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A library scanner logs a student ID every time a book is checked out, and the same student may appear more than once in the day's log.
+```python
 attendees = {"A101", "A102", "A101", "A103"}
 print(len(attendees))
 ```
@@ -1584,7 +1585,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A movie ticketing app starts building a collection of booked seat numbers but the developer types an empty pair of curly braces instead of using set().
+```python
 empty = {}
 print(type(empty))
 ```
@@ -1666,7 +1668,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A hospital intake system stores visiting patient IDs for the day in a set and a nurse tries to grab the first ID the same way she would from a list.
+```python
 attendees = {"A101", "A102", "A103"}
 print(attendees[0])
 ```
@@ -1748,7 +1751,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A delivery app records every scan of a package's barcode as it moves through the warehouse, then converts the scan log into a set to see how many distinct packages were actually handled.
+```python
 scans = ["A101", "A102", "A101", "A103", "A101"]
 unique = set(scans)
 print(len(scans), len(unique))
@@ -1831,7 +1835,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>An esports platform tracks which player IDs logged in on each of two tournament days and wants to compare the day-1-only and day-2-only crowds.
+```python
 day1 = {"A101", "A102", "A103"}
 day2 = {"A103", "A104"}
 print(day1 - day2)
@@ -1915,7 +1920,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why is checking 'A101' in attendees on a set typically faster than checking the same value in a long list?</t>
+          <t>A social media app needs to check whether a given username already exists among millions of registered accounts stored either as a set or a list. Why is checking 'A101' in attendees on a set typically faster than checking the same value in a long list?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1993,7 +1998,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A developer wants 'attendees who only came on day 2' but writes day1 - day2 instead of day2 - day1. What is wrong with the result?</t>
+          <t>A conference app wants to find attendees who only came on the second day of a two-day event, using set subtraction on the day-1 and day-2 ID sets. A developer wants 'attendees who only came on day 2' but writes day1 - day2 instead of day2 - day1. What is wrong with the result?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2071,7 +2076,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A campus fest app wants to know which attendee IDs showed up on both day 1 and day 2 of the event.
+```python
 day1 = {"A101", "A102", "A103"}
 day2 = {"A103", "A104"}
 print(day1 &amp; day2)
@@ -2154,7 +2160,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>An online store keeps a small price list and a cashier needs to look up the price of one item at checkout.
+```python
 prices = {"T-shirt": 350, "Mug": 150}
 print(prices["Mug"])
 ```
@@ -2236,7 +2243,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A fest organizer wants attendees who came on exactly one of the two days, not both, using the symmetric difference of the day-1 and day-2 ID sets.
+```python
 day1 = {"A101", "A102", "A103"}
 day2 = {"A103", "A104"}
 print(day1 ^ day2)
@@ -2420,7 +2428,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A retail billing app looks up a price dictionary for a checkout scan, but the scanned item was never actually stocked.
+```python
 prices = {"T-shirt": 350, "Mug": 150}
 print(prices["Cap"])
 ```
@@ -2502,7 +2511,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gym's membership pricing sheet needs its "Mug" merchandise price updated after a supplier changes rates, using the same key that was originally used to add the item.
+```python
 prices = {"Mug": 150}
 prices["Mug"] = 180
 print(prices)
@@ -2585,7 +2595,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A canteen stock system needs to discontinue the "Cap" item and wants to both remove it from the stock dictionary and know how many were left in stock at the time.
+```python
 stock = {"Mug": 15, "Cap": 20}
 removed = stock.pop("Cap")
 print(removed, stock)
@@ -2668,7 +2679,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shopkeeper's price dictionary maps item names to their prices, and a new hire mistakenly tries to check if the price 350 itself is a valid item name.
+```python
 prices = {"T-shirt": 350, "Mug": 150}
 print(350 in prices)
 ```
@@ -2750,7 +2762,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>An event merchandise stall wants a quick count of how many distinct items are on its price list before printing the day's menu board.
+```python
 prices = {"T-shirt": 350, "Mug": 150, "Badge": 50}
 print(len(prices))
 ```
@@ -2832,7 +2845,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A pop-up stall adds a brand-new item, "Cap", to its price list partway through the day using a key that didn't exist before.
+```python
 prices = {"T-shirt": 350, "Mug": 150}
 prices["Cap"] = 200
 print(prices)
@@ -2915,7 +2929,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A vending kiosk wants to safely look up an item's price and just show 0 if that item isn't stocked, instead of the app crashing on unknown items.
+```python
 prices = {"Mug": 150}
 print(prices.get("Cap", 0))
 ```
@@ -2997,7 +3012,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A store clerk tries to remove an item that was never actually added to the stall's price dictionary in the first place.
+```python
 prices = {"Mug": 150}
 del prices["Cap"]
 ```
@@ -3079,7 +3095,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A stall owner wants to print every item in the price list alongside its price to hand out as a quick reference sheet.
+```python
 prices = {"Mug": 150, "Badge": 50}
 for item, price in prices.items():
     print(item, price)
@@ -3162,7 +3179,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shopkeeper wants the end-of-day stock report printed in alphabetical order by item name rather than the order items happen to appear in the dictionary.
+```python
 stock = {"Badge": 25, "T-shirt": 12, "Mug": 8}
 for item, count in sorted(stock.items()):
     print(item, count)
@@ -3346,7 +3364,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A developer writes for item in prices: `print(item, prices[item])` instead of for item, price in `prices.items()`: `print(item, price)`. What is the main downside of the first version?</t>
+          <t>A pricing report needs both the item name and its price on every line, but a developer writes it using only the keys and a separate lookup, instead of the more direct .items() approach.
+A developer writes for item in prices: `print(item, prices[item])` instead of for item, price in `prices.items()`: `print(item, price)`. What is the main downside of the first version?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3424,7 +3443,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A developer wants to print every price but mistakenly writes for price in `prices.keys()`: `print(price)`. What actually gets printed?</t>
+          <t>A billing script tries to print every price in a shop's price list but loops over the wrong part of the dictionary by mistake.
+A developer wants to print every price but mistakenly writes for price in `prices.keys()`: `print(price)`. What actually gets printed?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3502,7 +3522,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shop owner wants a quick list of every item name currently on the price board, without needing the prices themselves.
+```python
 prices = {"T-shirt": 350, "Mug": 150}
 for item in prices:
     print(item)
@@ -3585,7 +3606,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A festive sale offers 20% off every item, so a stall builds a new discounted price dictionary from the original one in a single comprehension.
+```python
 prices = {"Mug": 150, "Badge": 50}
 discounted = {item: price * 0.8 for item, price in prices.items()}
 ```
@@ -3667,7 +3689,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>An inventory app has two separate lists, item names and their prices, and wants to combine them into one dictionary in a single line using zip.
+```python
 items = ["Mug", "Badge"]
 prices_list = [150, 50]
 result = {item: price for item, price in zip(items, prices_list)}
@@ -3750,7 +3773,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A fest coordinator raises the price of Samosa at the Food stall mid-event by updating the nested dictionary that stores prices per stall.
+```python
 fest_stalls = {"Food": {"Samosa": 30}, "Games": {"Dart": 25}}
 fest_stalls["Food"]["Samosa"] = 35
 print(fest_stalls)
@@ -3833,7 +3857,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A fest coordinator wants a full printed report of every stall along with every item and price sold at that stall, looping through the nested price dictionary.
+```python
 fest_stalls = {"Food": {"Samosa": 30}, "Games": {"Dart": 25}}
 for stall, items in fest_stalls.items():
     for item, price in items.items():
@@ -3917,7 +3942,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A customer at the Food stall asks for the price of "Lemonade", but that item was never added to the Food stall's nested price dictionary.
+```python
 fest_stalls = {"Food": {"Samosa": 30}}
 print(fest_stalls["Food"]["Lemonade"])
 ```
@@ -3999,7 +4025,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A stall wants a report of only its premium items, defined as anything priced 100 or more, built directly from the full price dictionary using a comprehension.
+```python
 prices = {"Mug": 150, "Badge": 50, "Cap": 200}
 result = {item: price for item, price in prices.items() if price &gt;= 100}
 ```
@@ -4081,7 +4108,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A naming system tries to build a quick lookup dictionary keyed by each word's first letter, from a small list of words.
+```python
 words = ["cat", "car", "dog"]
 result = {w[0]: w for w in words}
 ```

--- a/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 7.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 7.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 7.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 7.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 7.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 7.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 7.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 7.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,17 +643,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>A list, since it preserves every entry</t>
+          <t>A set, since it automatically removes duplicate values</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>A set, since it automatically removes duplicate values</t>
+          <t>A string, since it stores characters</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>A string, since it stores characters</t>
+          <t>A list, since it preserves every single entry</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -727,26 +727,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Only A101 and A102</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Only A104 shown</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Only A103 shown</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Only A101 and A102</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>A101, A102, A103, A104</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Only A104 shown</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -810,21 +810,21 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>prices = {"Mug": 150, "Badge": 50}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>prices = {"Mug", 150, "Badge", 50}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>prices = ["Mug", 150, "Badge", 50]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>prices = {"Mug", 150, "Badge", 50}</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>prices = {"Mug": 150, "Badge": 50}</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -888,26 +888,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`KeyError`</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>{'Samosa': 30, 'Cold Drink': 40}</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>`KeyError`</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -966,26 +966,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Switch the prices variable entirely from a dictionary into a plain list instead</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Wrap the whole loop in a try/except that does nothing on error</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Use del `prices[item]` right before doing the lookup each time</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Use `prices.get(item, 0)` so missing items safely contribute 0 instead of crashing</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Wrap the whole loop in a try/except that does nothing on error</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Switch the prices variable entirely from a dictionary into a list</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1049,26 +1049,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>{'T-shirt': 12, 'Badge': 25}</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>An empty dictionary</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{'Mug': 0, 'Cap': 0}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>The full original dictionary, unchanged</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>An empty dictionary</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{'Mug': 0, 'Cap': 0}</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>{'T-shirt': 12, 'Badge': 25}</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>A list for submissions, a tuple for scores</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>A set for submissions, a dictionary for scores</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A tuple for both, since neither should change</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>A dictionary for submissions, a set for scores</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>A list for submissions, a tuple for scores</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>A tuple for both, since neither should change</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1215,16 +1215,16 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Symmetric difference, since it excludes anyone in both sets</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Difference, since order does not matter here</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Symmetric difference, since it excludes anyone in both sets</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Error, `sum()` cannot be used on dict values</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Error, `sum()` cannot be used on dict values</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>450</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1371,22 +1371,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>`SyntaxError`</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>{'Mug': 200}</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'Mug': 150, 'Mug': 200}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>{'Mug': 150}</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>{'Mug': 200}</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>`SyntaxError`</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>{'Mug': 150, 'Mug': 200}</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1555,26 +1555,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1638,26 +1638,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>&lt;class 'set'&gt;, because curly braces always mean a set</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>&lt;class 'dict'&gt;, because empty curly braces create a dictionary, not a set</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>A `SyntaxError` is raised, since {} is considered invalid</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>&lt;class 'list'&gt;, because Python simply defaults to a list here</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>&lt;class 'set'&gt;, because curly braces always mean a set</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It raises an `IndexError`, same as an empty list</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It prints the first item inserted</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>It prints 'A101' because sets are sorted alphabetically</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>It raises a `TypeError`, since sets are not indexable</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It prints the first item inserted</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It raises an `IndexError`, same as an empty list</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It prints 'A101' because sets are sorted alphabetically</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>3 5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>3 3</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3 5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Empty set both times</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>{'A104'} then {'A101', 'A102'}</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Empty set both times</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sets technically only ever allow checking the very first element</t>
+          <t>Sets are always stored permanently on disk instead of in memory</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sets are always stored permanently on disk instead of in memory</t>
+          <t>Sets technically only ever allow checking the very first element that was inserted</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2046,26 +2046,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>It technically raises a `TypeError`, since sets cannot be subtracted at all</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>It actually returns who only attended day 1, the opposite of the intended question</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>It technically raises a `TypeError`, since sets cannot be subtracted at all</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>It simply returns the attendees from both days combined together</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Nothing is wrong, difference is symmetric so order does not matter</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>It simply returns the attendees from both days combined together</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2130,26 +2130,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>{'A101', 'A102', 'A103', 'A104'}</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>{'A101', 'A102'}</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>{'A103'}</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>{'A101', 'A102', 'A103', 'A104'}</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>{'A101', 'A102'}</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>{'A104'}</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2213,26 +2213,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>`KeyError`</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>"Mug"</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>`KeyError`</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>"Mug"</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>{'A103'}</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Empty set</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>{'A101', 'A102', 'A103', 'A104'}</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{'A103'}</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Empty set</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2481,26 +2481,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It prints 0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>It silently adds 'Cap' with a value of `None`</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It raises a `KeyError`</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>It prints `None`</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>It raises a `KeyError`</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It silently adds 'Cap' with a value of `None`</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It prints 0</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>{'Mug': 150}</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{'Mug': 150, 'Mug': 180}</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>`KeyError`, since Mug already exists</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>{'Mug': 150, 'Mug': 180}</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>{'Mug': 150}</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2649,26 +2649,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>20 {'Mug': 15}</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>`None` {'Mug': 15, 'Cap': 20}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>20 {'Mug': 15, 'Cap': 20}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Cap {'Mug': 15}</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>20 {'Mug': 15}</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>20 {'Mug': 15, 'Cap': 20}</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>`None` {'Mug': 15, 'Cap': 20}</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2732,22 +2732,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>It raises a `TypeError`, since you cannot check a number</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`False`, because in checks keys, and 350 is a value, not a key</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>`True`, because dictionaries check both keys and values</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>`False`, because in checks keys, and 350 is a value, not a key</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>`True`, because 350 appears as a value</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>It raises a `TypeError`, since you cannot check a number</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2815,26 +2815,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Error, `len()` does not work on dictionaries</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Error, `len()` does not work on dictionaries</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Error, since Cap was never declared beforehand</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>{'T-shirt': 350, 'Mug': 150, 'Cap': 200}</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Error, since Cap was never declared beforehand</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>{'T-shirt': 350, 'Mug': 150} unchanged</t>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2987,21 +2987,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>`None`</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>`KeyError`</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>`KeyError`</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>`None`</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>T-shirt, Mug, Badge (reverse insertion)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Sorted by count value, ascending</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Badge, T-shirt, Mug (insertion order)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>T-shirt, Mug, Badge (reverse insertion)</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Sorted by count value, ascending</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>It only ever works correctly if the dictionary has fewer than 10 keys total</t>
+          <t>It only ever works correctly if the dictionary happens to have fewer than 10 keys total</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3492,26 +3492,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>The prices are printed, exactly as originally intended</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The item names (keys), not the prices, despite the variable name</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A `TypeError` occurs, since `keys()` cannot be looped over at all</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>An empty result is returned, since `keys()` returns nothing</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>A `TypeError` occurs, since `keys()` cannot be looped over at all</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>The item names (keys), not the prices, despite the variable name</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>The prices are printed, exactly as originally intended</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3576,26 +3576,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>T-shirt then Mug</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Just the first key, T-shirt</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>('T-shirt', 350) then ('Mug', 150)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>350 then 150</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>T-shirt then Mug</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Just the first key, T-shirt</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3659,26 +3659,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>An error, comprehensions cannot use `.items()`</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>{'Mug': 150, 'Badge': 50}</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>An error, comprehensions cannot use `.items()`</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>{'Mug': 0.8, 'Badge': 0.8}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>{'Mug': 120.0, 'Badge': 40.0}</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>{'Mug': 0.8, 'Badge': 0.8}</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3743,26 +3743,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>An error, zip cannot be used inside a comprehension</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>[('Mug', 150), ('Badge', 50)]</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>{'Mug': 150, 'Badge': 50}</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>{150: 'Mug', 50: 'Badge'}</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>An error, zip cannot be used inside a comprehension</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3827,26 +3827,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>An error, nested values cannot be updated directly</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>{'Food': {'Samosa': 35}, 'Games': {'Dart': 25}}</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{'Samosa': 35}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>{'Food': {'Samosa': 30}, 'Games': {'Dart': 25}}</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>{'Samosa': 35}</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{'Food': {'Samosa': 35}, 'Games': {'Dart': 25}}</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>An error, nested values cannot be updated directly</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3912,26 +3912,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Food Samosa 30 then Games Dart 25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>An error, since `items()` cannot be called twice</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Only Food Samosa 30 is printed</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Food Games then Samosa Dart</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Food Samosa 30 then Games Dart 25</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>An error, since `items()` cannot be called twice</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Only Food Samosa 30 is printed</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3995,26 +3995,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It silently prints the value `None` instead</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>It raises a `KeyError`, best fixed with `.get()` on the inner dictionary</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>It silently prints the value `None` instead</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>It raises an `IndexError`, since nested lookups use position</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>It automatically returns 0 without raising any error</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>It raises an `IndexError`, since nested lookups use position</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4078,26 +4078,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>{'Mug': 150, 'Badge': 50, 'Cap': 200}</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>{'Mug': 1, 'Cap': 1}</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{'Badge': 50}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>{'Mug': 150, 'Cap': 200}</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>{'Mug': 1, 'Cap': 1}</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>{'Badge': 50}</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>{'Mug': 150, 'Badge': 50, 'Cap': 200}</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4161,26 +4161,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>{'c': 'car', 'd': 'dog'}, because the later 'c' key overwrites the earlier one</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>{'c': 'cat', 'c': 'car', 'd': 'dog'}, three entries</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'c': 'cat', 'd': 'dog'}, because the first matching key always wins here</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>An error, since two words cannot share a first letter</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>{'c': 'car', 'd': 'dog'}, because the later 'c' key overwrites the earlier one</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{'c': 'cat', 'd': 'dog'}, because the first match always wins</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>{'c': 'cat', 'c': 'car', 'd': 'dog'}, three entries</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The union operator | combines both sets into one, keeping every value that appears in either set while counting any shared value, here A103, only once.</t>
+          <t>The union operator | combines both sets into one, keeping every value that appears in either set while counting any shared value, here `A103`, only once.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -727,22 +727,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Only A101 and A102</t>
+          <t>Only `A101` and `A102`</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Only A104 shown</t>
+          <t>Only `A104` shown</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Only A103 shown</t>
+          <t>Only `A103` shown</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A101, A102, A103, A104</t>
+          <t>`A101`, `A102`, `A103`, `A104`</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1001,7 +1001,7 @@
 stock = {"T-shirt": 12, "Mug": 0, "Badge": 25, "Cap": 0}
 in_stock = {item: count for item, count in stock.items() if count &gt; 0}
 ```
-What does in_stock contain?</t>
+What does `in_stock` contain?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The set literal collapses the repeated 'A101' into a single entry, so the set holds three unique IDs, A101, A102, and A103, and `len()` reports 3.</t>
+          <t>The set literal collapses the repeated '`A101`' into a single entry, so the set holds three unique IDs, `A101`, `A102`, and `A103`, and `len()` reports 3.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A movie ticketing app starts building a collection of booked seat numbers but the developer types an empty pair of curly braces instead of using set().
+          <t>A movie ticketing app starts building a collection of booked seat numbers but the developer types an empty pair of curly braces instead of using `set()`.
 ```python
 empty = {}
 print(type(empty))
@@ -1731,7 +1731,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>It prints 'A101' because sets are sorted alphabetically</t>
+          <t>It prints '`A101`' because sets are sorted alphabetically</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scans keeps all 5 entries including repeats, while converting it to a set collapses the three repeated 'A101' entries into one, leaving 3 unique IDs: A101, A102, A103.</t>
+          <t>scans keeps all 5 entries including repeats, while converting it to a set collapses the three repeated '`A101`' entries into one, leaving 3 unique IDs: `A101`, `A102`, `A103`.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>day1 - day2 keeps values in day1 that are not in day2, giving A101 and A102; day2 - day1 keeps values in day2 not in day1, giving A104, so swapping the operands swaps the result entirely.</t>
+          <t>day1 - day2 keeps values in day1 that are not in day2, giving `A101` and `A102`; day2 - day1 keeps values in day2 not in day1, giving `A104`, so swapping the operands swaps the result entirely.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{'A101', 'A102'} then {'A104'}</t>
+          <t>{'`A101`', '`A102`'} then {'`A104`'}</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>{'A104'} then {'A101', 'A102'}</t>
+          <t>{'`A104`'} then {'`A101`', '`A102`'}</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>{'A103'} both times</t>
+          <t>{'`A103`'} both times</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A social media app needs to check whether a given username already exists among millions of registered accounts stored either as a set or a list. Why is checking 'A101' in attendees on a set typically faster than checking the same value in a long list?</t>
+          <t>A social media app needs to check whether a given username already exists among millions of registered accounts stored either as a set or a list. Why is checking '`A101`' in attendees on a set typically faster than checking the same value in a long list?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The intersection operator &amp; keeps only the values present in both sets; A103 is the only ID that appears in both day1 and day2, so the result is {'A103'}.</t>
+          <t>The intersection operator &amp; keeps only the values present in both sets; `A103` is the only ID that appears in both day1 and day2, so the result is {'`A103`'}.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2130,22 +2130,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{'A101', 'A102', 'A103', 'A104'}</t>
+          <t>{'`A101`', '`A102`', '`A103`', '`A104`'}</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>{'A101', 'A102'}</t>
+          <t>{'`A101`', '`A102`'}</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>{'A103'}</t>
+          <t>{'`A103`'}</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>{'A104'}</t>
+          <t>{'`A104`'}</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Symmetric difference (^) keeps values that are in exactly one of the two sets but not both; A103 is in both so it is excluded, leaving A101, A102, and A104.</t>
+          <t>Symmetric difference (^) keeps values that are in exactly one of the two sets but not both; `A103` is in both so it is excluded, leaving `A101`, `A102`, and `A104`.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{'A101', 'A102', 'A104'}</t>
+          <t>{'`A101`', '`A102`', '`A104`'}</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{'A103'}</t>
+          <t>{'`A103`'}</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>{'A101', 'A102', 'A103', 'A104'}</t>
+          <t>{'`A101`', '`A102`', '`A103`', '`A104`'}</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A pricing report needs both the item name and its price on every line, but a developer writes it using only the keys and a separate lookup, instead of the more direct .items() approach.
+          <t>A pricing report needs both the item name and its price on every line, but a developer writes it using only the keys and a separate lookup, instead of the more direct .`items()` approach.
 A developer writes for item in prices: `print(item, prices[item])` instead of for item, price in `prices.items()`: `print(item, price)`. What is the main downside of the first version?</t>
         </is>
       </c>

--- a/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - MCQ.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The union operator | combines both sets into one, keeping every value that appears in either set while counting any shared value, here `A103`, only once.</t>
+          <t>The union operator `|` combines both sets into one, keeping every value that appears in either set while counting any shared value, here `A103`, only once.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A developer writes total = total + `prices[item]` inside a loop, but some items are not guaranteed to be in prices, causing intermittent KeyErrors. What is the safest minimal fix?</t>
+          <t>A developer writes `total = total + prices[item]` inside a loop, but some items are not guaranteed to be in `prices`, causing intermittent `KeyError`s. What is the safest minimal fix?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Use del `prices[item]` right before doing the lookup each time</t>
+          <t>Use `del prices[item]` right before doing the lookup each time</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Symmetric difference (^ or `.symmetric_difference()`) is defined precisely as values in either set but not both, which is exactly 'attended exactly one day, not both', avoiding a manual union-minus-intersection computation.</t>
+          <t>Symmetric difference (`^` or `.symmetric_difference()`) is defined precisely as values in either set but not both, which is exactly 'attended exactly one day, not both', avoiding a manual union-minus-intersection computation.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A social media app needs to check whether a given username already exists among millions of registered accounts stored either as a set or a list. Why is checking '`A101`' in attendees on a set typically faster than checking the same value in a long list?</t>
+          <t>A social media app needs to check whether a given username already exists among millions of registered accounts stored either as a set or a list. Why is checking `'A101' in attendees` on a set typically faster than checking the same value in a long list?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A conference app wants to find attendees who only came on the second day of a two-day event, using set subtraction on the day-1 and day-2 ID sets. A developer wants 'attendees who only came on day 2' but writes day1 - day2 instead of day2 - day1. What is wrong with the result?</t>
+          <t>A conference app wants to find attendees who only came on the second day of a two-day event, using set subtraction on the day-1 and day-2 ID sets. A developer wants 'attendees who only came on day 2' but writes `day1 - day2` instead of `day2 - day1`. What is wrong with the result?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3364,8 +3364,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A pricing report needs both the item name and its price on every line, but a developer writes it using only the keys and a separate lookup, instead of the more direct .`items()` approach.
-A developer writes for item in prices: `print(item, prices[item])` instead of for item, price in `prices.items()`: `print(item, price)`. What is the main downside of the first version?</t>
+          <t>A pricing report needs both the item name and its price on every line, but a developer writes it using only the keys and a separate lookup, instead of the more direct `.items()` approach.
+A developer writes `for item in prices: print(item, prices[item])` instead of `for item, price in prices.items(): print(item, price)`. What is the main downside of the first version?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>A billing script tries to print every price in a shop's price list but loops over the wrong part of the dictionary by mistake.
-A developer wants to print every price but mistakenly writes for price in `prices.keys()`: `print(price)`. What actually gets printed?</t>
+A developer wants to print every price but mistakenly writes `for price in prices.keys(): print(price)`. What actually gets printed?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Looking up 'Lemonade' in the inner Food dictionary raises a `KeyError` since that key was never added there; the safest fix is to use `fest_stalls['Food']``.get('Lemonade', 0)` or check 'Lemonade' in `fest_stalls['Food']` before indexing.</t>
+          <t>Looking up 'Lemonade' in the inner Food dictionary raises a `KeyError` since that key was never added there; the safest fix is to use `fest_stalls['Food'].get('Lemonade', 0)` or check `'Lemonade' in fest_stalls['Food']` before indexing.</t>
         </is>
       </c>
       <c r="D9" t="n">
